--- a/KnowledgeSystem/AppResources/317/Templates/TE-701-T001-05 冶金部技術工程師評鑑結果彙總表.xlsx
+++ b/KnowledgeSystem/AppResources/317/Templates/TE-701-T001-05 冶金部技術工程師評鑑結果彙總表.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\1.經理室\00組務\00歷年文件\6.張氏水\2026年技術工程師評鑑 作業標準修訂\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\01. DEV\01.7System\01.Projects\7system\KnowledgeSystem\AppResources\317\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00642B3-F320-42DD-9B63-6929C7E95930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="7245"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -17,17 +18,29 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">工作表1!$A$1:$K$26</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <r>
       <t>Bảng Tổng hợp K</t>
@@ -446,10 +459,6 @@
     </r>
   </si>
   <si>
-    <t>經理室</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve"> </t>
     </r>
@@ -524,19 +533,6 @@
         <charset val="136"/>
       </rPr>
       <t>五</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>規計處</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -544,11 +540,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="17">
     <font>
       <sz val="13"/>
       <color theme="1"/>
@@ -635,10 +631,26 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="新細明體"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="標楷體"/>
+      <family val="4"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="4">
@@ -718,15 +730,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -736,24 +739,33 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -785,7 +797,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="圖片 2"/>
+        <xdr:cNvPr id="2" name="圖片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -1090,12 +1108,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K20"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="15.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.77734375" style="1" customWidth="1"/>
@@ -1108,43 +1126,43 @@
     <col min="12" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="J1" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="K1" s="13"/>
-    </row>
-    <row r="2" spans="1:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+    <row r="1" spans="1:11" ht="17.25">
+      <c r="J1" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="10"/>
+    </row>
+    <row r="2" spans="1:11" ht="21">
+      <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-    </row>
-    <row r="3" spans="1:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+    </row>
+    <row r="3" spans="1:11" ht="21">
+      <c r="A3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-    </row>
-    <row r="4" spans="1:11" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+    </row>
+    <row r="4" spans="1:11" ht="20.25">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -1155,13 +1173,13 @@
       <c r="F4" s="3"/>
       <c r="G4" s="4"/>
       <c r="H4" s="5"/>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-    </row>
-    <row r="5" spans="1:11" s="2" customFormat="1" ht="89.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+    </row>
+    <row r="5" spans="1:11" s="2" customFormat="1" ht="89.65" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>1</v>
       </c>
@@ -1196,206 +1214,195 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+    <row r="6" spans="1:11" ht="19.5">
+      <c r="A6" s="15"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="16"/>
+    </row>
+    <row r="7" spans="1:11" ht="18.75">
+      <c r="A7" s="18"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="16"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="14"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="J20" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="18">
-        <f>G6*0.2+H6*0.3+I6*0.5</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="17"/>
-    </row>
-    <row r="7" spans="1:11" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="18">
-        <f t="shared" ref="J7" si="0">G7*0.2+H7*0.3+I7*0.5</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="17"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="9"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J20" s="8" t="s">
-        <v>16</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="G8:H8"/>
+  <mergeCells count="4">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="J1:K1"/>
